--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,26 +542,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-513</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8890</v>
+        <v>19277</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13289</v>
+        <v>22922</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4399</v>
+        <v>-3645</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>13-JUN-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,30 +587,30 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-764</t>
+          <t>Nile Air NP-143</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>10736</v>
+        <v>16232</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13289</v>
+        <v>19236</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-2553</v>
+        <v>-3004</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>08-AUG-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,30 +632,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-513</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6637</v>
+        <v>13784</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6817</v>
+        <v>19236</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-180</v>
+        <v>-5452</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,26 +677,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8818</v>
+        <v>13707</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9508</v>
+        <v>16232</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-690</v>
+        <v>-2525</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7107</v>
+        <v>13324</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7217</v>
+        <v>16232</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-110</v>
+        <v>-2908</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -743,9 +743,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,26 +767,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-143</t>
+          <t>Air Arabia Egypt E5-511</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7245</v>
+        <v>14219</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>7521</v>
+        <v>16232</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-276</v>
+        <v>-2013</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -794,366 +794,6 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>23-JUL-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-511</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>9071</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>13289</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-4218</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25-JUL-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-513</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>8890</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>13289</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-4399</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-511</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>9329</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>13289</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-3960</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-143</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>8266</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>13289</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-5023</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>30-JUL-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-511</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>10621</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>13289</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-2668</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-511</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>8813</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>13289</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-4476</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>17-SEP-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-756</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>11012</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>13289</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-2277</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19-SEP-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-443</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-513</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>8890</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>13289</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-4399</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_CAI_AHB_threats.xlsx
+++ b/excel_routes/route_CAI_AHB_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6335F7-D99B-48F6-8066-D6EF3938A20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C294D19C-A11A-40B4-BC12-B19AA3B62E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="43">
   <si>
     <t>Date</t>
   </si>
@@ -78,6 +78,9 @@
     <t>30-JUL-26</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
     <t>08-AUG-26</t>
   </si>
   <si>
@@ -96,6 +99,9 @@
     <t>12-AUG-26</t>
   </si>
   <si>
+    <t>27-AUG-26</t>
+  </si>
+  <si>
     <t>29-AUG-26</t>
   </si>
   <si>
@@ -121,9 +127,6 @@
   </si>
   <si>
     <t>28-OCT-26</t>
-  </si>
-  <si>
-    <t>HIGH</t>
   </si>
   <si>
     <t>04-NOV-26</t>
@@ -198,14 +201,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor rgb="FFF8D7DA"/>
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -556,7 +559,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -617,10 +620,10 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>19277</v>
+        <v>19276</v>
       </c>
       <c r="E2" s="2">
-        <v>22922</v>
+        <v>22921</v>
       </c>
       <c r="F2" s="2">
         <v>-3645</v>
@@ -655,10 +658,10 @@
         <v>16232</v>
       </c>
       <c r="E3" s="2">
-        <v>19236</v>
+        <v>22921</v>
       </c>
       <c r="F3" s="2">
-        <v>-3004</v>
+        <v>-6689</v>
       </c>
       <c r="G3" s="2">
         <v>30</v>
@@ -669,8 +672,8 @@
       <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>14</v>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>15</v>
@@ -678,22 +681,22 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2">
-        <v>13788</v>
+        <v>13733</v>
       </c>
       <c r="E4" s="2">
-        <v>19236</v>
+        <v>19235</v>
       </c>
       <c r="F4" s="2">
-        <v>-5448</v>
+        <v>-5502</v>
       </c>
       <c r="G4" s="2">
         <v>20</v>
@@ -713,22 +716,22 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2">
-        <v>13712</v>
+        <v>13657</v>
       </c>
       <c r="E5" s="2">
         <v>16232</v>
       </c>
       <c r="F5" s="2">
-        <v>-2520</v>
+        <v>-2575</v>
       </c>
       <c r="G5" s="2">
         <v>20</v>
@@ -739,8 +742,8 @@
       <c r="I5" s="2">
         <v>10</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>21</v>
+      <c r="J5" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>15</v>
@@ -748,7 +751,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -783,22 +786,22 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2">
-        <v>14812</v>
+        <v>14677</v>
       </c>
       <c r="E7" s="2">
-        <v>19236</v>
+        <v>16232</v>
       </c>
       <c r="F7" s="2">
-        <v>-4424</v>
+        <v>-1555</v>
       </c>
       <c r="G7" s="2">
         <v>20</v>
@@ -809,8 +812,8 @@
       <c r="I7" s="2">
         <v>10</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>14</v>
+      <c r="J7" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -818,22 +821,22 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2">
-        <v>13200</v>
+        <v>14753</v>
       </c>
       <c r="E8" s="2">
-        <v>16232</v>
+        <v>19235</v>
       </c>
       <c r="F8" s="2">
-        <v>-3032</v>
+        <v>-4482</v>
       </c>
       <c r="G8" s="2">
         <v>20</v>
@@ -844,8 +847,8 @@
       <c r="I8" s="2">
         <v>10</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>21</v>
+      <c r="J8" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>15</v>
@@ -853,22 +856,22 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2">
-        <v>12205</v>
+        <v>13147</v>
       </c>
       <c r="E9" s="2">
         <v>16232</v>
       </c>
       <c r="F9" s="2">
-        <v>-4027</v>
+        <v>-3085</v>
       </c>
       <c r="G9" s="2">
         <v>20</v>
@@ -879,8 +882,8 @@
       <c r="I9" s="2">
         <v>10</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>21</v>
+      <c r="J9" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>15</v>
@@ -888,34 +891,34 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D10" s="2">
-        <v>11331</v>
+        <v>12157</v>
       </c>
       <c r="E10" s="2">
-        <v>13242</v>
+        <v>16232</v>
       </c>
       <c r="F10" s="2">
-        <v>-1911</v>
+        <v>-4075</v>
       </c>
       <c r="G10" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2">
         <v>30</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>15</v>
@@ -923,7 +926,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -932,13 +935,13 @@
         <v>13</v>
       </c>
       <c r="D11" s="2">
-        <v>9570</v>
+        <v>11331</v>
       </c>
       <c r="E11" s="2">
         <v>13242</v>
       </c>
       <c r="F11" s="2">
-        <v>-3672</v>
+        <v>-1911</v>
       </c>
       <c r="G11" s="2">
         <v>30</v>
@@ -949,8 +952,8 @@
       <c r="I11" s="2">
         <v>0</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>14</v>
+      <c r="J11" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>15</v>
@@ -958,31 +961,31 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2">
-        <v>7568</v>
+        <v>9570</v>
       </c>
       <c r="E12" s="2">
         <v>13242</v>
       </c>
       <c r="F12" s="2">
-        <v>-5674</v>
+        <v>-3672</v>
       </c>
       <c r="G12" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2">
         <v>30</v>
       </c>
       <c r="I12" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>14</v>
@@ -993,22 +996,22 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D13" s="2">
-        <v>7645</v>
+        <v>7309</v>
       </c>
       <c r="E13" s="2">
         <v>13242</v>
       </c>
       <c r="F13" s="2">
-        <v>-5597</v>
+        <v>-5933</v>
       </c>
       <c r="G13" s="2">
         <v>20</v>
@@ -1028,34 +1031,34 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D14" s="2">
-        <v>7058</v>
+        <v>7615</v>
       </c>
       <c r="E14" s="2">
-        <v>7153</v>
+        <v>13242</v>
       </c>
       <c r="F14" s="2">
-        <v>-95</v>
+        <v>-5627</v>
       </c>
       <c r="G14" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2">
         <v>30</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>21</v>
+        <v>10</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>15</v>
@@ -1063,34 +1066,34 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D15" s="2">
-        <v>7338</v>
+        <v>7058</v>
       </c>
       <c r="E15" s="2">
-        <v>22922</v>
+        <v>7153</v>
       </c>
       <c r="F15" s="2">
-        <v>-15584</v>
+        <v>-95</v>
       </c>
       <c r="G15" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2">
         <v>30</v>
       </c>
       <c r="I15" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>15</v>
@@ -1104,16 +1107,16 @@
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D16" s="2">
-        <v>7338</v>
+        <v>7309</v>
       </c>
       <c r="E16" s="2">
-        <v>22922</v>
+        <v>22921</v>
       </c>
       <c r="F16" s="2">
-        <v>-15584</v>
+        <v>-15612</v>
       </c>
       <c r="G16" s="2">
         <v>20</v>
@@ -1124,8 +1127,8 @@
       <c r="I16" s="2">
         <v>10</v>
       </c>
-      <c r="J16" s="5" t="s">
-        <v>32</v>
+      <c r="J16" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>15</v>
@@ -1139,16 +1142,16 @@
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D17" s="2">
-        <v>7338</v>
+        <v>7309</v>
       </c>
       <c r="E17" s="2">
-        <v>22922</v>
+        <v>22921</v>
       </c>
       <c r="F17" s="2">
-        <v>-15584</v>
+        <v>-15612</v>
       </c>
       <c r="G17" s="2">
         <v>20</v>
@@ -1159,8 +1162,8 @@
       <c r="I17" s="2">
         <v>10</v>
       </c>
-      <c r="J17" s="5" t="s">
-        <v>32</v>
+      <c r="J17" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>15</v>
@@ -1174,16 +1177,16 @@
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" s="2">
-        <v>7338</v>
+        <v>7309</v>
       </c>
       <c r="E18" s="2">
-        <v>22922</v>
+        <v>22921</v>
       </c>
       <c r="F18" s="2">
-        <v>-15584</v>
+        <v>-15612</v>
       </c>
       <c r="G18" s="2">
         <v>20</v>
@@ -1194,8 +1197,8 @@
       <c r="I18" s="2">
         <v>10</v>
       </c>
-      <c r="J18" s="5" t="s">
-        <v>32</v>
+      <c r="J18" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>15</v>
@@ -1209,16 +1212,16 @@
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" s="2">
-        <v>7338</v>
+        <v>7309</v>
       </c>
       <c r="E19" s="2">
-        <v>22922</v>
+        <v>22921</v>
       </c>
       <c r="F19" s="2">
-        <v>-15584</v>
+        <v>-15612</v>
       </c>
       <c r="G19" s="2">
         <v>20</v>
@@ -1229,8 +1232,8 @@
       <c r="I19" s="2">
         <v>10</v>
       </c>
-      <c r="J19" s="5" t="s">
-        <v>32</v>
+      <c r="J19" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>15</v>
@@ -1244,16 +1247,16 @@
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D20" s="2">
-        <v>7338</v>
+        <v>7309</v>
       </c>
       <c r="E20" s="2">
-        <v>22922</v>
+        <v>22921</v>
       </c>
       <c r="F20" s="2">
-        <v>-15584</v>
+        <v>-15612</v>
       </c>
       <c r="G20" s="2">
         <v>20</v>
@@ -1264,8 +1267,8 @@
       <c r="I20" s="2">
         <v>10</v>
       </c>
-      <c r="J20" s="5" t="s">
-        <v>32</v>
+      <c r="J20" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>15</v>
@@ -1279,16 +1282,16 @@
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D21" s="2">
-        <v>7338</v>
+        <v>7309</v>
       </c>
       <c r="E21" s="2">
-        <v>22922</v>
+        <v>22921</v>
       </c>
       <c r="F21" s="2">
-        <v>-15584</v>
+        <v>-15612</v>
       </c>
       <c r="G21" s="2">
         <v>20</v>
@@ -1299,8 +1302,8 @@
       <c r="I21" s="2">
         <v>10</v>
       </c>
-      <c r="J21" s="5" t="s">
-        <v>32</v>
+      <c r="J21" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>15</v>
@@ -1314,16 +1317,16 @@
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D22" s="2">
-        <v>7338</v>
+        <v>7309</v>
       </c>
       <c r="E22" s="2">
-        <v>22922</v>
+        <v>22921</v>
       </c>
       <c r="F22" s="2">
-        <v>-15584</v>
+        <v>-15612</v>
       </c>
       <c r="G22" s="2">
         <v>20</v>
@@ -1334,8 +1337,8 @@
       <c r="I22" s="2">
         <v>10</v>
       </c>
-      <c r="J22" s="5" t="s">
-        <v>32</v>
+      <c r="J22" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>15</v>
@@ -1349,16 +1352,16 @@
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D23" s="2">
-        <v>7338</v>
+        <v>7309</v>
       </c>
       <c r="E23" s="2">
-        <v>22922</v>
+        <v>22921</v>
       </c>
       <c r="F23" s="2">
-        <v>-15584</v>
+        <v>-15612</v>
       </c>
       <c r="G23" s="2">
         <v>20</v>
@@ -1369,8 +1372,8 @@
       <c r="I23" s="2">
         <v>10</v>
       </c>
-      <c r="J23" s="5" t="s">
-        <v>32</v>
+      <c r="J23" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>15</v>
@@ -1384,16 +1387,16 @@
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24" s="2">
-        <v>7338</v>
+        <v>7309</v>
       </c>
       <c r="E24" s="2">
-        <v>22922</v>
+        <v>22921</v>
       </c>
       <c r="F24" s="2">
-        <v>-15584</v>
+        <v>-15612</v>
       </c>
       <c r="G24" s="2">
         <v>20</v>
@@ -1404,10 +1407,45 @@
       <c r="I24" s="2">
         <v>10</v>
       </c>
-      <c r="J24" s="5" t="s">
-        <v>32</v>
+      <c r="J24" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K24" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="2">
+        <v>7309</v>
+      </c>
+      <c r="E25" s="2">
+        <v>22921</v>
+      </c>
+      <c r="F25" s="2">
+        <v>-15612</v>
+      </c>
+      <c r="G25" s="2">
+        <v>20</v>
+      </c>
+      <c r="H25" s="2">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2">
+        <v>10</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>15</v>
       </c>
     </row>
